--- a/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0001T0006Z000C1N39_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0001T0006Z000C1N39_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.18513407559329</v>
+        <v>5.555084287283909</v>
       </c>
       <c r="D2" t="n">
-        <v>35.61073373672462</v>
+        <v>5.78674423221775</v>
       </c>
       <c r="E2" t="n">
-        <v>10.83400626415007</v>
+        <v>1.760526017924387</v>
       </c>
       <c r="F2" t="n">
-        <v>11.28071395088756</v>
+        <v>1.833116017019228</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.35365185083134</v>
+        <v>5.257468425760093</v>
       </c>
       <c r="D3" t="n">
-        <v>32.51530530428168</v>
+        <v>5.283737111945772</v>
       </c>
       <c r="E3" t="n">
-        <v>10.83400626415007</v>
+        <v>1.760526017924387</v>
       </c>
       <c r="F3" t="n">
-        <v>11.28071395088756</v>
+        <v>1.833116017019228</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.19290563537665</v>
+        <v>2.956347165748705</v>
       </c>
       <c r="D4" t="n">
-        <v>18.45738257690738</v>
+        <v>2.999324668747449</v>
       </c>
       <c r="E4" t="n">
-        <v>10.83400626415007</v>
+        <v>1.760526017924387</v>
       </c>
       <c r="F4" t="n">
-        <v>11.28071395088756</v>
+        <v>1.833116017019228</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>14.15259191767238</v>
+        <v>2.299796186621762</v>
       </c>
       <c r="D5" t="n">
-        <v>13.87403944740807</v>
+        <v>2.254531410203812</v>
       </c>
       <c r="E5" t="n">
-        <v>10.83400626415007</v>
+        <v>1.760526017924387</v>
       </c>
       <c r="F5" t="n">
-        <v>11.28071395088756</v>
+        <v>1.833116017019228</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>5.854964184417084</v>
+        <v>0.9514316799677762</v>
       </c>
       <c r="D6" t="n">
-        <v>5.72801282916796</v>
+        <v>0.9308020847397935</v>
       </c>
       <c r="E6" t="n">
-        <v>10.83400626415007</v>
+        <v>1.760526017924387</v>
       </c>
       <c r="F6" t="n">
-        <v>11.28071395088756</v>
+        <v>1.833116017019228</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
